--- a/ESERCIZIO_M2-2-3_dati.xlsx
+++ b/ESERCIZIO_M2-2-3_dati.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E0EE70-0DCE-40A4-A2C4-50D63BF184D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C30D5D6-8A76-4454-8D97-148C293856D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pivot Vendite" sheetId="4" r:id="rId1"/>
     <sheet name="Vendite" sheetId="1" r:id="rId2"/>
-    <sheet name="Pivot Performances" sheetId="5" r:id="rId3"/>
+    <sheet name="Pivot Performances" sheetId="6" r:id="rId3"/>
     <sheet name="Performances" sheetId="2" r:id="rId4"/>
     <sheet name="Social Media" sheetId="3" r:id="rId5"/>
   </sheets>
@@ -26,6 +26,7 @@
     <definedName name="COD_PRODOTTO">Vendite!$B$2:$B$1048576</definedName>
     <definedName name="Codice">#REF!</definedName>
     <definedName name="DANIELE">#REF!</definedName>
+    <definedName name="FiltroDati_Media_valutazioni">#N/A</definedName>
     <definedName name="ID">Vendite!$A$2:$A$1048576</definedName>
     <definedName name="IMPO">#REF!</definedName>
     <definedName name="IMPORTO">#REF!</definedName>
@@ -39,19 +40,27 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId7"/>
-    <pivotCache cacheId="25" r:id="rId8"/>
+    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="10" r:id="rId8"/>
   </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId9"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="zoeLcdjU48/pMIVB+XP18tPgVIVpOBsIviNr/EZwH9M="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataChecksum="zoeLcdjU48/pMIVB+XP18tPgVIVpOBsIviNr/EZwH9M="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="140">
   <si>
     <t>CATEGORIA PRODOTTO</t>
   </si>
@@ -458,15 +467,6 @@
     <t>Somma di VENDITE</t>
   </si>
   <si>
-    <t>Media di Valutazione delle Prestazioni</t>
-  </si>
-  <si>
-    <t>Media di Valutazione dell'Anno Precedente</t>
-  </si>
-  <si>
-    <t>Somma di Differenza valutazioni</t>
-  </si>
-  <si>
     <t>Crescita Followers</t>
   </si>
   <si>
@@ -474,6 +474,12 @@
   </si>
   <si>
     <t>Somma like e commenti</t>
+  </si>
+  <si>
+    <t>Media valutazioni</t>
+  </si>
+  <si>
+    <t>Somma di Media valutazioni</t>
   </si>
 </sst>
 </file>
@@ -562,7 +568,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -592,14 +598,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -607,11 +611,12 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -625,22 +630,6 @@
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1931,6 +1920,89 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>336550</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>41272</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Media valutazioni">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5057AE6E-9283-A4F0-67A5-A41446AB3BB6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Media valutazioni"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3416300" y="514350"/>
+              <a:ext cx="1828800" cy="2333622"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="it-IT" sz="1100"/>
+                <a:t>Questa forma rappresenta un filtro dei dati. I filtri dei dati sono supportati in Excel 2010 o versione successiva.
+Se la forma è stata modificata in una versione precedente di Excel o se la cartella di lavoro è stata salvata in Excel 2003 o versioni precedenti, non è possibile usare il filtro dei dati.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
@@ -2029,23 +2101,78 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Lenovo" refreshedDate="46083.710945254628" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="61" xr:uid="{DC5F1E74-BF72-4BFC-BFB0-7948A2D18D87}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Lenovo" refreshedDate="46084.81253333333" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="61" xr:uid="{047214B5-5F22-4C23-801A-9F445F9271F6}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:D1048576" sheet="Performances"/>
+    <worksheetSource ref="A1:E1048576" sheet="Performances"/>
   </cacheSource>
-  <cacheFields count="7">
+  <cacheFields count="5">
     <cacheField name="Codice Dipendente" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="101" maxValue="160"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="101" maxValue="160" count="61">
+        <n v="101"/>
+        <n v="102"/>
+        <n v="103"/>
+        <n v="104"/>
+        <n v="105"/>
+        <n v="106"/>
+        <n v="107"/>
+        <n v="108"/>
+        <n v="109"/>
+        <n v="110"/>
+        <n v="111"/>
+        <n v="112"/>
+        <n v="113"/>
+        <n v="114"/>
+        <n v="115"/>
+        <n v="116"/>
+        <n v="117"/>
+        <n v="118"/>
+        <n v="119"/>
+        <n v="120"/>
+        <n v="121"/>
+        <n v="122"/>
+        <n v="123"/>
+        <n v="124"/>
+        <n v="125"/>
+        <n v="126"/>
+        <n v="127"/>
+        <n v="128"/>
+        <n v="129"/>
+        <n v="130"/>
+        <n v="131"/>
+        <n v="132"/>
+        <n v="133"/>
+        <n v="134"/>
+        <n v="135"/>
+        <n v="136"/>
+        <n v="137"/>
+        <n v="138"/>
+        <n v="139"/>
+        <n v="140"/>
+        <n v="141"/>
+        <n v="142"/>
+        <n v="143"/>
+        <n v="144"/>
+        <n v="145"/>
+        <n v="146"/>
+        <n v="147"/>
+        <n v="148"/>
+        <n v="149"/>
+        <n v="150"/>
+        <n v="151"/>
+        <n v="152"/>
+        <n v="153"/>
+        <n v="154"/>
+        <n v="155"/>
+        <n v="156"/>
+        <n v="157"/>
+        <n v="158"/>
+        <n v="159"/>
+        <n v="160"/>
+        <m/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Dipartimento" numFmtId="0">
-      <sharedItems containsBlank="1" count="6">
-        <s v="Vendite"/>
-        <s v="Risorse Umane"/>
-        <s v="IT"/>
-        <s v="Finanza"/>
-        <s v="Marketing"/>
-        <m/>
-      </sharedItems>
+      <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Valutazione delle Prestazioni" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="3.3" maxValue="4.9000000000000004"/>
@@ -2053,13 +2180,34 @@
     <cacheField name="Valutazione dell'Anno Precedente" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="3.1" maxValue="4.5999999999999996"/>
     </cacheField>
-    <cacheField name="Differenza valutazione" numFmtId="0" formula="'Valutazione delle Prestazioni' -'Valutazione dell''Anno Precedente'" databaseField="0"/>
-    <cacheField name="differenza valutazioni delle prestazioni anno" numFmtId="0" formula="'Valutazione delle Prestazioni' -'Valutazione dell''Anno Precedente'" databaseField="0"/>
-    <cacheField name="Differenza valutazioni" numFmtId="0" formula="'Valutazione delle Prestazioni' -'Valutazione dell''Anno Precedente'" databaseField="0"/>
+    <cacheField name="Media valutazioni" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="3.2" maxValue="4.75" count="20">
+        <n v="4.3499999999999996"/>
+        <n v="3.7"/>
+        <n v="4.0999999999999996"/>
+        <n v="4.6500000000000004"/>
+        <n v="3.4"/>
+        <n v="3.9"/>
+        <n v="3.6"/>
+        <n v="3.8"/>
+        <n v="4.1999999999999993"/>
+        <n v="3.5"/>
+        <n v="4"/>
+        <n v="4.5500000000000007"/>
+        <n v="3.3"/>
+        <n v="4.25"/>
+        <n v="4.4499999999999993"/>
+        <n v="4.3000000000000007"/>
+        <n v="4.75"/>
+        <n v="3.2"/>
+        <n v="4.1500000000000004"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
+      <x14:pivotCacheDefinition pivotCacheId="772740843"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -16758,376 +16906,437 @@
 <file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="61">
   <r>
-    <n v="101"/>
     <x v="0"/>
+    <s v="Vendite"/>
     <n v="4.5"/>
     <n v="4.2"/>
-  </r>
-  <r>
-    <n v="102"/>
+    <x v="0"/>
+  </r>
+  <r>
     <x v="1"/>
+    <s v="Risorse Umane"/>
     <n v="3.8"/>
     <n v="3.6"/>
-  </r>
-  <r>
-    <n v="103"/>
+    <x v="1"/>
+  </r>
+  <r>
     <x v="2"/>
+    <s v="IT"/>
     <n v="4.2"/>
     <n v="4"/>
-  </r>
-  <r>
-    <n v="104"/>
+    <x v="2"/>
+  </r>
+  <r>
     <x v="3"/>
+    <s v="Finanza"/>
     <n v="4.8"/>
     <n v="4.5"/>
-  </r>
-  <r>
-    <n v="105"/>
+    <x v="3"/>
+  </r>
+  <r>
     <x v="4"/>
+    <s v="Marketing"/>
     <n v="3.5"/>
     <n v="3.3"/>
-  </r>
-  <r>
-    <n v="106"/>
-    <x v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="Vendite"/>
     <n v="4"/>
     <n v="3.8"/>
-  </r>
-  <r>
-    <n v="107"/>
-    <x v="1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <s v="Risorse Umane"/>
     <n v="3.7"/>
     <n v="3.5"/>
-  </r>
-  <r>
-    <n v="108"/>
-    <x v="2"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="IT"/>
     <n v="4.5"/>
     <n v="4.2"/>
-  </r>
-  <r>
-    <n v="109"/>
-    <x v="3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="Finanza"/>
     <n v="4.2"/>
     <n v="4"/>
-  </r>
-  <r>
-    <n v="110"/>
-    <x v="4"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="Marketing"/>
     <n v="3.9"/>
     <n v="3.7"/>
-  </r>
-  <r>
-    <n v="111"/>
-    <x v="0"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <s v="Vendite"/>
     <n v="4.3"/>
     <n v="4.0999999999999996"/>
-  </r>
-  <r>
-    <n v="112"/>
-    <x v="1"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <s v="Risorse Umane"/>
     <n v="3.6"/>
     <n v="3.4"/>
-  </r>
-  <r>
-    <n v="113"/>
-    <x v="2"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <s v="IT"/>
     <n v="4.0999999999999996"/>
     <n v="3.9"/>
-  </r>
-  <r>
-    <n v="114"/>
-    <x v="3"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <s v="Finanza"/>
     <n v="4.7"/>
     <n v="4.4000000000000004"/>
-  </r>
-  <r>
-    <n v="115"/>
-    <x v="4"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <s v="Marketing"/>
     <n v="3.4"/>
     <n v="3.2"/>
-  </r>
-  <r>
-    <n v="116"/>
-    <x v="0"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <s v="Vendite"/>
     <n v="4.2"/>
     <n v="4"/>
-  </r>
-  <r>
-    <n v="117"/>
-    <x v="1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <s v="Risorse Umane"/>
     <n v="3.9"/>
     <n v="3.7"/>
-  </r>
-  <r>
-    <n v="118"/>
-    <x v="2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <s v="IT"/>
     <n v="4.4000000000000004"/>
     <n v="4.0999999999999996"/>
-  </r>
-  <r>
-    <n v="119"/>
-    <x v="3"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <s v="Finanza"/>
     <n v="4.5999999999999996"/>
     <n v="4.3"/>
-  </r>
-  <r>
-    <n v="120"/>
-    <x v="4"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <s v="Marketing"/>
     <n v="3.6"/>
     <n v="3.4"/>
-  </r>
-  <r>
-    <n v="121"/>
-    <x v="0"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <s v="Vendite"/>
     <n v="4.0999999999999996"/>
     <n v="3.9"/>
-  </r>
-  <r>
-    <n v="122"/>
-    <x v="1"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <s v="Risorse Umane"/>
     <n v="3.8"/>
     <n v="3.6"/>
-  </r>
-  <r>
-    <n v="123"/>
-    <x v="2"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="22"/>
+    <s v="IT"/>
     <n v="4.3"/>
     <n v="4.0999999999999996"/>
-  </r>
-  <r>
-    <n v="124"/>
-    <x v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="23"/>
+    <s v="Finanza"/>
     <n v="4.5"/>
     <n v="4.2"/>
-  </r>
-  <r>
-    <n v="125"/>
-    <x v="4"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="24"/>
+    <s v="Marketing"/>
     <n v="3.7"/>
     <n v="3.5"/>
-  </r>
-  <r>
-    <n v="126"/>
-    <x v="0"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="25"/>
+    <s v="Vendite"/>
     <n v="3.9"/>
     <n v="3.7"/>
-  </r>
-  <r>
-    <n v="127"/>
-    <x v="1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="26"/>
+    <s v="Risorse Umane"/>
     <n v="3.5"/>
     <n v="3.3"/>
-  </r>
-  <r>
-    <n v="128"/>
-    <x v="2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="27"/>
+    <s v="IT"/>
     <n v="4"/>
     <n v="3.8"/>
-  </r>
-  <r>
-    <n v="129"/>
-    <x v="3"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="28"/>
+    <s v="Finanza"/>
     <n v="4.4000000000000004"/>
     <n v="4.2"/>
-  </r>
-  <r>
-    <n v="130"/>
-    <x v="4"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="29"/>
+    <s v="Marketing"/>
     <n v="3.8"/>
     <n v="3.6"/>
-  </r>
-  <r>
-    <n v="131"/>
-    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="30"/>
+    <s v="Vendite"/>
     <n v="4.5999999999999996"/>
     <n v="4.3"/>
-  </r>
-  <r>
-    <n v="132"/>
-    <x v="1"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="31"/>
+    <s v="Risorse Umane"/>
     <n v="3.7"/>
     <n v="3.5"/>
-  </r>
-  <r>
-    <n v="133"/>
-    <x v="2"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="32"/>
+    <s v="IT"/>
     <n v="4.2"/>
     <n v="4"/>
-  </r>
-  <r>
-    <n v="134"/>
-    <x v="3"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="33"/>
+    <s v="Finanza"/>
     <n v="4.9000000000000004"/>
     <n v="4.5999999999999996"/>
-  </r>
-  <r>
-    <n v="135"/>
-    <x v="4"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="34"/>
+    <s v="Marketing"/>
     <n v="3.3"/>
     <n v="3.1"/>
-  </r>
-  <r>
-    <n v="136"/>
-    <x v="0"/>
+    <x v="17"/>
+  </r>
+  <r>
+    <x v="35"/>
+    <s v="Vendite"/>
     <n v="4.4000000000000004"/>
     <n v="4.0999999999999996"/>
-  </r>
-  <r>
-    <n v="137"/>
-    <x v="1"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="36"/>
+    <s v="Risorse Umane"/>
     <n v="3.6"/>
     <n v="3.4"/>
-  </r>
-  <r>
-    <n v="138"/>
-    <x v="2"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="37"/>
+    <s v="IT"/>
     <n v="4.3"/>
     <n v="4"/>
-  </r>
-  <r>
-    <n v="139"/>
-    <x v="3"/>
+    <x v="18"/>
+  </r>
+  <r>
+    <x v="38"/>
+    <s v="Finanza"/>
     <n v="4.8"/>
     <n v="4.5"/>
-  </r>
-  <r>
-    <n v="140"/>
-    <x v="4"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="39"/>
+    <s v="Marketing"/>
     <n v="3.5"/>
     <n v="3.3"/>
-  </r>
-  <r>
-    <n v="141"/>
-    <x v="0"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="40"/>
+    <s v="Vendite"/>
     <n v="4"/>
     <n v="3.8"/>
-  </r>
-  <r>
-    <n v="142"/>
-    <x v="1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="41"/>
+    <s v="Risorse Umane"/>
     <n v="3.9"/>
     <n v="3.7"/>
-  </r>
-  <r>
-    <n v="143"/>
-    <x v="2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="42"/>
+    <s v="IT"/>
     <n v="4.0999999999999996"/>
     <n v="3.9"/>
-  </r>
-  <r>
-    <n v="144"/>
-    <x v="3"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="43"/>
+    <s v="Finanza"/>
     <n v="4.7"/>
     <n v="4.4000000000000004"/>
-  </r>
-  <r>
-    <n v="145"/>
-    <x v="4"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="44"/>
+    <s v="Marketing"/>
     <n v="3.4"/>
     <n v="3.2"/>
-  </r>
-  <r>
-    <n v="146"/>
-    <x v="0"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="45"/>
+    <s v="Vendite"/>
     <n v="4.2"/>
     <n v="4"/>
-  </r>
-  <r>
-    <n v="147"/>
-    <x v="1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="46"/>
+    <s v="Risorse Umane"/>
     <n v="3.9"/>
     <n v="3.7"/>
-  </r>
-  <r>
-    <n v="148"/>
-    <x v="2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="47"/>
+    <s v="IT"/>
     <n v="4.5"/>
     <n v="4.2"/>
-  </r>
-  <r>
-    <n v="149"/>
-    <x v="3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="48"/>
+    <s v="Finanza"/>
     <n v="4.2"/>
     <n v="4"/>
-  </r>
-  <r>
-    <n v="150"/>
-    <x v="4"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="49"/>
+    <s v="Marketing"/>
     <n v="3.8"/>
     <n v="3.6"/>
-  </r>
-  <r>
-    <n v="151"/>
-    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="50"/>
+    <s v="Vendite"/>
     <n v="4.3"/>
     <n v="4.0999999999999996"/>
-  </r>
-  <r>
-    <n v="152"/>
-    <x v="1"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="51"/>
+    <s v="Risorse Umane"/>
     <n v="3.6"/>
     <n v="3.4"/>
-  </r>
-  <r>
-    <n v="153"/>
-    <x v="2"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="52"/>
+    <s v="IT"/>
     <n v="4.0999999999999996"/>
     <n v="3.9"/>
-  </r>
-  <r>
-    <n v="154"/>
-    <x v="3"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="53"/>
+    <s v="Finanza"/>
     <n v="4.7"/>
     <n v="4.4000000000000004"/>
-  </r>
-  <r>
-    <n v="155"/>
-    <x v="4"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="54"/>
+    <s v="Marketing"/>
     <n v="3.4"/>
     <n v="3.2"/>
-  </r>
-  <r>
-    <n v="156"/>
-    <x v="0"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="55"/>
+    <s v="Vendite"/>
     <n v="4.2"/>
     <n v="4"/>
-  </r>
-  <r>
-    <n v="157"/>
-    <x v="1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="56"/>
+    <s v="Risorse Umane"/>
     <n v="3.9"/>
     <n v="3.7"/>
-  </r>
-  <r>
-    <n v="158"/>
-    <x v="2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="57"/>
+    <s v="IT"/>
     <n v="4.4000000000000004"/>
     <n v="4.0999999999999996"/>
-  </r>
-  <r>
-    <n v="159"/>
-    <x v="3"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="58"/>
+    <s v="Finanza"/>
     <n v="4.5999999999999996"/>
     <n v="4.3"/>
-  </r>
-  <r>
-    <n v="160"/>
-    <x v="4"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="59"/>
+    <s v="Marketing"/>
     <n v="3.6"/>
     <n v="3.4"/>
-  </r>
-  <r>
-    <m/>
-    <x v="5"/>
-    <m/>
-    <m/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="60"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="19"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04E53C1E-F57D-4C7D-8332-14F6F022DA78}" name="Tabella pivot2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04E53C1E-F57D-4C7D-8332-14F6F022DA78}" name="Tabella pivot2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B83" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -17502,36 +17711,110 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{945EF912-56C5-4184-831B-C3DAF4B4BE5C}" name="Tabella pivot3" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:D10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="7">
-    <pivotField showAll="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1229DAC9-9EF7-46B3-A315-3A854F20CCB6}" name="Tabella pivot1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B36" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
-      <items count="7">
+      <items count="62">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
         <item x="3"/>
-        <item x="2"/>
         <item x="4"/>
-        <item x="1"/>
-        <item x="0"/>
         <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="21">
+        <item h="1" x="17"/>
+        <item h="1" x="12"/>
+        <item h="1" x="4"/>
+        <item h="1" x="9"/>
+        <item h="1" x="6"/>
+        <item h="1" x="1"/>
+        <item h="1" x="7"/>
+        <item h="1" x="5"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="18"/>
+        <item x="8"/>
+        <item x="13"/>
+        <item x="15"/>
+        <item x="0"/>
+        <item x="14"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="16"/>
+        <item h="1" x="19"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="1"/>
+    <field x="0"/>
   </rowFields>
-  <rowItems count="7">
+  <rowItems count="33">
     <i>
       <x/>
-    </i>
-    <i>
-      <x v="1"/>
     </i>
     <i>
       <x v="2"/>
@@ -17540,94 +17823,102 @@
       <x v="3"/>
     </i>
     <i>
-      <x v="4"/>
+      <x v="7"/>
     </i>
     <i>
-      <x v="5"/>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="37"/>
+    </i>
+    <i>
+      <x v="38"/>
+    </i>
+    <i>
+      <x v="42"/>
+    </i>
+    <i>
+      <x v="43"/>
+    </i>
+    <i>
+      <x v="45"/>
+    </i>
+    <i>
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="48"/>
+    </i>
+    <i>
+      <x v="50"/>
+    </i>
+    <i>
+      <x v="52"/>
+    </i>
+    <i>
+      <x v="53"/>
+    </i>
+    <i>
+      <x v="55"/>
+    </i>
+    <i>
+      <x v="57"/>
+    </i>
+    <i>
+      <x v="58"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
+  <colItems count="1">
+    <i/>
   </colItems>
-  <dataFields count="3">
-    <dataField name="Media di Valutazione delle Prestazioni" fld="2" subtotal="average" baseField="1" baseItem="3"/>
-    <dataField name="Media di Valutazione dell'Anno Precedente" fld="3" subtotal="average" baseField="1" baseItem="2"/>
-    <dataField name="Somma di Differenza valutazioni" fld="6" baseField="1" baseItem="0" numFmtId="9"/>
+  <dataFields count="1">
+    <dataField name="Somma di Media valutazioni" fld="4" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="3">
-    <format dxfId="5">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="1" count="5">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="4">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-          <reference field="1" count="5">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="3">
-      <pivotArea outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <conditionalFormats count="1">
-    <conditionalFormat priority="1">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="1" count="5">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-  </conditionalFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -17638,6 +17929,46 @@
     </ext>
   </extLst>
 </pivotTableDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="FiltroDati_Media_valutazioni" xr10:uid="{0C3FB23E-03E2-4ED3-9F56-CE607974F869}" sourceName="Media valutazioni">
+  <pivotTables>
+    <pivotTable tabId="6" name="Tabella pivot1"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="772740843">
+      <items count="20">
+        <i x="17"/>
+        <i x="12"/>
+        <i x="4"/>
+        <i x="9"/>
+        <i x="6"/>
+        <i x="1"/>
+        <i x="7"/>
+        <i x="5"/>
+        <i x="10" s="1"/>
+        <i x="2" s="1"/>
+        <i x="18" s="1"/>
+        <i x="8" s="1"/>
+        <i x="13" s="1"/>
+        <i x="15" s="1"/>
+        <i x="0" s="1"/>
+        <i x="14" s="1"/>
+        <i x="11" s="1"/>
+        <i x="3" s="1"/>
+        <i x="16" s="1"/>
+        <i x="19" nd="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Media valutazioni" xr10:uid="{E12254DE-BEE3-4554-8B0B-99D4A00F94CD}" cache="FiltroDati_Media_valutazioni" caption="Media valutazioni" startItem="13" rowHeight="220133"/>
+</slicers>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17857,87 +18188,87 @@
       <c r="A4" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4">
         <v>344000</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5">
         <v>45000</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6">
         <v>48000</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7">
         <v>45000</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8">
         <v>17000</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9">
         <v>32000</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10">
         <v>22000</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11">
         <v>36000</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12">
         <v>60000</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13">
         <v>11000</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14">
         <v>28000</v>
       </c>
     </row>
@@ -17945,87 +18276,87 @@
       <c r="A15" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15">
         <v>438000</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16">
         <v>84000</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17">
         <v>48000</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18">
         <v>24000</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19">
         <v>30000</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20">
         <v>67000</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21">
         <v>50000</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22">
         <v>28000</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23">
         <v>9000</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24">
         <v>15000</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25">
         <v>83000</v>
       </c>
     </row>
@@ -18033,87 +18364,87 @@
       <c r="A26" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26">
         <v>370000</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27">
         <v>15000</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B28" s="15">
+      <c r="B28">
         <v>11000</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B29" s="15">
+      <c r="B29">
         <v>28000</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="16" t="s">
+      <c r="A30" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B30" s="15">
+      <c r="B30">
         <v>75000</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B31" s="15">
+      <c r="B31">
         <v>24000</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="16" t="s">
+      <c r="A32" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="15">
+      <c r="B32">
         <v>46000</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B33" s="15">
+      <c r="B33">
         <v>65000</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B34" s="15">
+      <c r="B34">
         <v>26000</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B35" s="15">
+      <c r="B35">
         <v>52000</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B36" s="15">
+      <c r="B36">
         <v>28000</v>
       </c>
     </row>
@@ -18121,87 +18452,87 @@
       <c r="A37" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="15">
+      <c r="B37">
         <v>359000</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B38" s="15">
+      <c r="B38">
         <v>52000</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="16" t="s">
+      <c r="A39" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B39" s="15">
+      <c r="B39">
         <v>24000</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="16" t="s">
+      <c r="A40" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B40" s="15">
+      <c r="B40">
         <v>24000</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="16" t="s">
+      <c r="A41" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B41" s="15">
+      <c r="B41">
         <v>44000</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="16" t="s">
+      <c r="A42" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B42" s="15">
+      <c r="B42">
         <v>36000</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="16" t="s">
+      <c r="A43" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B43" s="15">
+      <c r="B43">
         <v>13000</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="16" t="s">
+      <c r="A44" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B44" s="15">
+      <c r="B44">
         <v>24000</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="16" t="s">
+      <c r="A45" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B45" s="15">
+      <c r="B45">
         <v>42000</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="16" t="s">
+      <c r="A46" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B46" s="15">
+      <c r="B46">
         <v>50000</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="16" t="s">
+      <c r="A47" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B47" s="15">
+      <c r="B47">
         <v>50000</v>
       </c>
     </row>
@@ -18209,87 +18540,87 @@
       <c r="A48" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B48" s="15">
+      <c r="B48">
         <v>331000</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="16" t="s">
+      <c r="A49" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B49" s="15">
+      <c r="B49">
         <v>22000</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="16" t="s">
+      <c r="A50" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B50" s="15">
+      <c r="B50">
         <v>28000</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="16" t="s">
+      <c r="A51" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B51" s="15">
+      <c r="B51">
         <v>10000</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="16" t="s">
+      <c r="A52" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B52" s="15">
+      <c r="B52">
         <v>22000</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="16" t="s">
+      <c r="A53" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B53" s="15">
+      <c r="B53">
         <v>45000</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="16" t="s">
+      <c r="A54" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B54" s="15">
+      <c r="B54">
         <v>58000</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="16" t="s">
+      <c r="A55" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B55" s="15">
+      <c r="B55">
         <v>25000</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="16" t="s">
+      <c r="A56" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B56" s="15">
+      <c r="B56">
         <v>29000</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="16" t="s">
+      <c r="A57" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B57" s="15">
+      <c r="B57">
         <v>50000</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="16" t="s">
+      <c r="A58" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B58" s="15">
+      <c r="B58">
         <v>42000</v>
       </c>
     </row>
@@ -18297,87 +18628,87 @@
       <c r="A59" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B59" s="15">
+      <c r="B59">
         <v>357000</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="16" t="s">
+      <c r="A60" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B60" s="15">
+      <c r="B60">
         <v>48000</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="16" t="s">
+      <c r="A61" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B61" s="15">
+      <c r="B61">
         <v>79000</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="16" t="s">
+      <c r="A62" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B62" s="15">
+      <c r="B62">
         <v>13000</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="16" t="s">
+      <c r="A63" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B63" s="15">
+      <c r="B63">
         <v>27000</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="16" t="s">
+      <c r="A64" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B64" s="15">
+      <c r="B64">
         <v>22000</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="16" t="s">
+      <c r="A65" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B65" s="15">
+      <c r="B65">
         <v>51000</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="16" t="s">
+      <c r="A66" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B66" s="15">
+      <c r="B66">
         <v>36000</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="16" t="s">
+      <c r="A67" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B67" s="15">
+      <c r="B67">
         <v>27000</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="16" t="s">
+      <c r="A68" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B68" s="15">
+      <c r="B68">
         <v>14000</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="16" t="s">
+      <c r="A69" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B69" s="15">
+      <c r="B69">
         <v>40000</v>
       </c>
     </row>
@@ -18385,87 +18716,87 @@
       <c r="A70" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B70" s="15">
+      <c r="B70">
         <v>344000</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="16" t="s">
+      <c r="A71" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B71" s="15">
+      <c r="B71">
         <v>21000</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="16" t="s">
+      <c r="A72" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B72" s="15">
+      <c r="B72">
         <v>24000</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="16" t="s">
+      <c r="A73" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B73" s="15">
+      <c r="B73">
         <v>72000</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="16" t="s">
+      <c r="A74" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="15">
+      <c r="B74">
         <v>49000</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="16" t="s">
+      <c r="A75" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B75" s="15">
+      <c r="B75">
         <v>17000</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="16" t="s">
+      <c r="A76" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B76" s="15">
+      <c r="B76">
         <v>49000</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="16" t="s">
+      <c r="A77" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B77" s="15">
+      <c r="B77">
         <v>38000</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="16" t="s">
+      <c r="A78" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B78" s="15">
+      <c r="B78">
         <v>29000</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="16" t="s">
+      <c r="A79" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B79" s="15">
+      <c r="B79">
         <v>19000</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="16" t="s">
+      <c r="A80" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B80" s="15">
+      <c r="B80">
         <v>26000</v>
       </c>
     </row>
@@ -18473,25 +18804,23 @@
       <c r="A81" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="B81" s="15"/>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" s="16" t="s">
+      <c r="A82" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="B82" s="15"/>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="B83" s="15">
+      <c r="B83">
         <v>2543000</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting pivot="1" sqref="B4 B15 B26 B37 B48 B59 B70">
-    <cfRule type="aboveAverage" dxfId="2" priority="1"/>
+    <cfRule type="aboveAverage" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -46254,131 +46583,296 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73E4FF79-65D7-4E95-9CB7-A62045B693EB}">
-  <dimension ref="A3:D10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA2A942C-36A2-4F43-A716-FEB19BEAD834}">
+  <dimension ref="A3:B36"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.09765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>131</v>
       </c>
       <c r="B3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="14">
+        <v>101</v>
+      </c>
+      <c r="B4" s="24">
+        <v>4.3499999999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="14">
+        <v>103</v>
+      </c>
+      <c r="B5" s="24">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="14">
+        <v>104</v>
+      </c>
+      <c r="B6" s="24">
+        <v>4.6500000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="14">
+        <v>108</v>
+      </c>
+      <c r="B7" s="24">
+        <v>4.3499999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="14">
+        <v>109</v>
+      </c>
+      <c r="B8" s="24">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="14">
+        <v>111</v>
+      </c>
+      <c r="B9" s="24">
+        <v>4.1999999999999993</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="14">
+        <v>113</v>
+      </c>
+      <c r="B10" s="24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="14">
+        <v>114</v>
+      </c>
+      <c r="B11" s="24">
+        <v>4.5500000000000007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="14">
+        <v>116</v>
+      </c>
+      <c r="B12" s="24">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="14">
+        <v>118</v>
+      </c>
+      <c r="B13" s="24">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="14">
+        <v>119</v>
+      </c>
+      <c r="B14" s="24">
+        <v>4.4499999999999993</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="14">
+        <v>121</v>
+      </c>
+      <c r="B15" s="24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="14">
+        <v>123</v>
+      </c>
+      <c r="B16" s="24">
+        <v>4.1999999999999993</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="14">
+        <v>124</v>
+      </c>
+      <c r="B17" s="24">
+        <v>4.3499999999999996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="14">
+        <v>129</v>
+      </c>
+      <c r="B18" s="24">
+        <v>4.3000000000000007</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="14">
+        <v>131</v>
+      </c>
+      <c r="B19" s="24">
+        <v>4.4499999999999993</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="14">
+        <v>133</v>
+      </c>
+      <c r="B20" s="24">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="14">
+        <v>134</v>
+      </c>
+      <c r="B21" s="24">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="14">
         <v>136</v>
       </c>
-      <c r="D3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="19">
-        <v>4.5916666666666668</v>
-      </c>
-      <c r="C4" s="19">
-        <v>4.3166666666666655</v>
-      </c>
-      <c r="D4" s="20">
-        <v>3.3000000000000114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="19">
-        <v>4.2583333333333337</v>
-      </c>
-      <c r="C5" s="19">
-        <v>4.0166666666666666</v>
-      </c>
-      <c r="D5" s="20">
-        <v>2.9000000000000057</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="19">
-        <v>3.5749999999999997</v>
-      </c>
-      <c r="C6" s="19">
-        <v>3.3750000000000004</v>
-      </c>
-      <c r="D6" s="20">
-        <v>2.3999999999999915</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="19">
-        <v>3.7416666666666667</v>
-      </c>
-      <c r="C7" s="19">
-        <v>3.5416666666666665</v>
-      </c>
-      <c r="D7" s="20">
-        <v>2.3999999999999986</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="19">
-        <v>4.2250000000000005</v>
-      </c>
-      <c r="C8" s="19">
+      <c r="B22" s="24">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="14">
+        <v>138</v>
+      </c>
+      <c r="B23" s="24">
+        <v>4.1500000000000004</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="14">
+        <v>139</v>
+      </c>
+      <c r="B24" s="24">
+        <v>4.6500000000000004</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="14">
+        <v>143</v>
+      </c>
+      <c r="B25" s="24">
         <v>4</v>
       </c>
-      <c r="D8" s="20">
-        <v>2.7000000000000028</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="14">
+        <v>144</v>
+      </c>
+      <c r="B26" s="24">
+        <v>4.5500000000000007</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="14">
+        <v>146</v>
+      </c>
+      <c r="B27" s="24">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="14">
+        <v>148</v>
+      </c>
+      <c r="B28" s="24">
+        <v>4.3499999999999996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="14">
+        <v>149</v>
+      </c>
+      <c r="B29" s="24">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="14">
+        <v>151</v>
+      </c>
+      <c r="B30" s="24">
+        <v>4.1999999999999993</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="14">
+        <v>153</v>
+      </c>
+      <c r="B31" s="24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="14">
+        <v>154</v>
+      </c>
+      <c r="B32" s="24">
+        <v>4.5500000000000007</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="14">
+        <v>156</v>
+      </c>
+      <c r="B33" s="24">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="14">
+        <v>158</v>
+      </c>
+      <c r="B34" s="24">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="14">
+        <v>159</v>
+      </c>
+      <c r="B35" s="24">
+        <v>4.4499999999999993</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="B10" s="15">
-        <v>4.078333333333334</v>
-      </c>
-      <c r="C10" s="15">
-        <v>3.8499999999999992</v>
-      </c>
-      <c r="D10" s="20">
-        <v>13.700000000000102</v>
+      <c r="B36" s="24">
+        <v>136.94999999999999</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting pivot="1" sqref="B4:B8">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId3"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -46387,15 +46881,16 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.296875" customWidth="1"/>
     <col min="3" max="3" width="27.69921875" customWidth="1"/>
     <col min="4" max="4" width="47.59765625" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>20</v>
       </c>
@@ -46408,845 +46903,1088 @@
       <c r="D1" s="10" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>101</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="18">
+      <c r="C2" s="17">
         <v>4.5</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="16">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="18">
+        <f>AVERAGE(C2,D2)</f>
+        <v>4.3499999999999996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>102</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="16">
         <v>3.8</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="16">
         <v>3.6</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E3" s="18">
+        <f t="shared" ref="E3:E61" si="0">AVERAGE(C3,D3)</f>
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>103</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="16">
         <v>4.2</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="16">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E4" s="18">
+        <f t="shared" si="0"/>
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>104</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="16">
         <v>4.8</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="16">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E5" s="18">
+        <f t="shared" si="0"/>
+        <v>4.6500000000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>105</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="16">
         <v>3.5</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="16">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E6" s="18">
+        <f t="shared" si="0"/>
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>106</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="16">
         <v>4</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="16">
         <v>3.8</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E7" s="18">
+        <f t="shared" si="0"/>
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>107</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="16">
         <v>3.7</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="16">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E8" s="18">
+        <f t="shared" si="0"/>
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>108</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="16">
         <v>4.5</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="16">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E9" s="18">
+        <f t="shared" si="0"/>
+        <v>4.3499999999999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>109</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="16">
         <v>4.2</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="16">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E10" s="18">
+        <f t="shared" si="0"/>
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>110</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="16">
         <v>3.9</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="16">
         <v>3.7</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E11" s="18">
+        <f t="shared" si="0"/>
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>111</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="16">
         <v>4.3</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="16">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E12" s="18">
+        <f t="shared" si="0"/>
+        <v>4.1999999999999993</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>112</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="16">
         <v>3.6</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="16">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E13" s="18">
+        <f t="shared" si="0"/>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>113</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="16">
         <v>4.0999999999999996</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="16">
         <v>3.9</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E14" s="18">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>114</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="16">
         <v>4.7</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="16">
         <v>4.4000000000000004</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E15" s="18">
+        <f t="shared" si="0"/>
+        <v>4.5500000000000007</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>115</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="16">
         <v>3.4</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="16">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="18">
+        <f t="shared" si="0"/>
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>116</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="16">
         <v>4.2</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="16">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E17" s="18">
+        <f t="shared" si="0"/>
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>117</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="16">
         <v>3.9</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="16">
         <v>3.7</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E18" s="18">
+        <f t="shared" si="0"/>
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>118</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="16">
         <v>4.4000000000000004</v>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="16">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E19" s="18">
+        <f t="shared" si="0"/>
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>119</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="16">
         <v>4.5999999999999996</v>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="16">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E20" s="18">
+        <f t="shared" si="0"/>
+        <v>4.4499999999999993</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>120</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="16">
         <v>3.6</v>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="16">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E21" s="18">
+        <f t="shared" si="0"/>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>121</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="16">
         <v>4.0999999999999996</v>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="16">
         <v>3.9</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E22" s="18">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>122</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="16">
         <v>3.8</v>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="16">
         <v>3.6</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E23" s="18">
+        <f t="shared" si="0"/>
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>123</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="16">
         <v>4.3</v>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="16">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E24" s="18">
+        <f t="shared" si="0"/>
+        <v>4.1999999999999993</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>124</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="16">
         <v>4.5</v>
       </c>
-      <c r="D25" s="17">
+      <c r="D25" s="16">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E25" s="18">
+        <f t="shared" si="0"/>
+        <v>4.3499999999999996</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>125</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="16">
         <v>3.7</v>
       </c>
-      <c r="D26" s="17">
+      <c r="D26" s="16">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E26" s="18">
+        <f t="shared" si="0"/>
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>126</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="17">
+      <c r="C27" s="16">
         <v>3.9</v>
       </c>
-      <c r="D27" s="17">
+      <c r="D27" s="16">
         <v>3.7</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E27" s="18">
+        <f t="shared" si="0"/>
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>127</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="17">
+      <c r="C28" s="16">
         <v>3.5</v>
       </c>
-      <c r="D28" s="17">
+      <c r="D28" s="16">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E28" s="18">
+        <f t="shared" si="0"/>
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>128</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="16">
         <v>4</v>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="16">
         <v>3.8</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E29" s="18">
+        <f t="shared" si="0"/>
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>129</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="17">
+      <c r="C30" s="16">
         <v>4.4000000000000004</v>
       </c>
-      <c r="D30" s="17">
+      <c r="D30" s="16">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E30" s="18">
+        <f t="shared" si="0"/>
+        <v>4.3000000000000007</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>130</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C31" s="17">
+      <c r="C31" s="16">
         <v>3.8</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="16">
         <v>3.6</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E31" s="18">
+        <f t="shared" si="0"/>
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>131</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C32" s="17">
+      <c r="C32" s="16">
         <v>4.5999999999999996</v>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="16">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E32" s="18">
+        <f t="shared" si="0"/>
+        <v>4.4499999999999993</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>132</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="17">
+      <c r="C33" s="16">
         <v>3.7</v>
       </c>
-      <c r="D33" s="17">
+      <c r="D33" s="16">
         <v>3.5</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E33" s="18">
+        <f t="shared" si="0"/>
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>133</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C34" s="17">
+      <c r="C34" s="16">
         <v>4.2</v>
       </c>
-      <c r="D34" s="17">
+      <c r="D34" s="16">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E34" s="18">
+        <f t="shared" si="0"/>
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>134</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C35" s="17">
+      <c r="C35" s="16">
         <v>4.9000000000000004</v>
       </c>
-      <c r="D35" s="17">
+      <c r="D35" s="16">
         <v>4.5999999999999996</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E35" s="18">
+        <f t="shared" si="0"/>
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>135</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C36" s="17">
+      <c r="C36" s="16">
         <v>3.3</v>
       </c>
-      <c r="D36" s="17">
+      <c r="D36" s="16">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E36" s="18">
+        <f t="shared" si="0"/>
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>136</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C37" s="17">
+      <c r="C37" s="16">
         <v>4.4000000000000004</v>
       </c>
-      <c r="D37" s="17">
+      <c r="D37" s="16">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E37" s="18">
+        <f t="shared" si="0"/>
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>137</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C38" s="17">
+      <c r="C38" s="16">
         <v>3.6</v>
       </c>
-      <c r="D38" s="17">
+      <c r="D38" s="16">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E38" s="18">
+        <f t="shared" si="0"/>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>138</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C39" s="17">
+      <c r="C39" s="16">
         <v>4.3</v>
       </c>
-      <c r="D39" s="17">
+      <c r="D39" s="16">
         <v>4</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E39" s="18">
+        <f t="shared" si="0"/>
+        <v>4.1500000000000004</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>139</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C40" s="17">
+      <c r="C40" s="16">
         <v>4.8</v>
       </c>
-      <c r="D40" s="17">
+      <c r="D40" s="16">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E40" s="18">
+        <f t="shared" si="0"/>
+        <v>4.6500000000000004</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>140</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C41" s="17">
+      <c r="C41" s="16">
         <v>3.5</v>
       </c>
-      <c r="D41" s="17">
+      <c r="D41" s="16">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E41" s="18">
+        <f t="shared" si="0"/>
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>141</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="17">
+      <c r="C42" s="16">
         <v>4</v>
       </c>
-      <c r="D42" s="17">
+      <c r="D42" s="16">
         <v>3.8</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E42" s="18">
+        <f t="shared" si="0"/>
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>142</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="17">
+      <c r="C43" s="16">
         <v>3.9</v>
       </c>
-      <c r="D43" s="17">
+      <c r="D43" s="16">
         <v>3.7</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E43" s="18">
+        <f t="shared" si="0"/>
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>143</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="17">
+      <c r="C44" s="16">
         <v>4.0999999999999996</v>
       </c>
-      <c r="D44" s="17">
+      <c r="D44" s="16">
         <v>3.9</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E44" s="18">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>144</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="17">
+      <c r="C45" s="16">
         <v>4.7</v>
       </c>
-      <c r="D45" s="17">
+      <c r="D45" s="16">
         <v>4.4000000000000004</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E45" s="18">
+        <f t="shared" si="0"/>
+        <v>4.5500000000000007</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>145</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C46" s="17">
+      <c r="C46" s="16">
         <v>3.4</v>
       </c>
-      <c r="D46" s="17">
+      <c r="D46" s="16">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E46" s="18">
+        <f t="shared" si="0"/>
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>146</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C47" s="17">
+      <c r="C47" s="16">
         <v>4.2</v>
       </c>
-      <c r="D47" s="17">
+      <c r="D47" s="16">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E47" s="18">
+        <f t="shared" si="0"/>
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>147</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C48" s="17">
+      <c r="C48" s="16">
         <v>3.9</v>
       </c>
-      <c r="D48" s="17">
+      <c r="D48" s="16">
         <v>3.7</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E48" s="18">
+        <f t="shared" si="0"/>
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>148</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C49" s="17">
+      <c r="C49" s="16">
         <v>4.5</v>
       </c>
-      <c r="D49" s="17">
+      <c r="D49" s="16">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E49" s="18">
+        <f t="shared" si="0"/>
+        <v>4.3499999999999996</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>149</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C50" s="17">
+      <c r="C50" s="16">
         <v>4.2</v>
       </c>
-      <c r="D50" s="17">
+      <c r="D50" s="16">
         <v>4</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E50" s="18">
+        <f t="shared" si="0"/>
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>150</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C51" s="17">
+      <c r="C51" s="16">
         <v>3.8</v>
       </c>
-      <c r="D51" s="17">
+      <c r="D51" s="16">
         <v>3.6</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E51" s="18">
+        <f t="shared" si="0"/>
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>151</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C52" s="17">
+      <c r="C52" s="16">
         <v>4.3</v>
       </c>
-      <c r="D52" s="17">
+      <c r="D52" s="16">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E52" s="18">
+        <f t="shared" si="0"/>
+        <v>4.1999999999999993</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>152</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C53" s="17">
+      <c r="C53" s="16">
         <v>3.6</v>
       </c>
-      <c r="D53" s="17">
+      <c r="D53" s="16">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E53" s="18">
+        <f t="shared" si="0"/>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>153</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C54" s="17">
+      <c r="C54" s="16">
         <v>4.0999999999999996</v>
       </c>
-      <c r="D54" s="17">
+      <c r="D54" s="16">
         <v>3.9</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E54" s="18">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>154</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C55" s="17">
+      <c r="C55" s="16">
         <v>4.7</v>
       </c>
-      <c r="D55" s="17">
+      <c r="D55" s="16">
         <v>4.4000000000000004</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E55" s="18">
+        <f t="shared" si="0"/>
+        <v>4.5500000000000007</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>155</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C56" s="17">
+      <c r="C56" s="16">
         <v>3.4</v>
       </c>
-      <c r="D56" s="17">
+      <c r="D56" s="16">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E56" s="18">
+        <f t="shared" si="0"/>
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>156</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C57" s="17">
+      <c r="C57" s="16">
         <v>4.2</v>
       </c>
-      <c r="D57" s="17">
+      <c r="D57" s="16">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E57" s="18">
+        <f t="shared" si="0"/>
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>157</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C58" s="17">
+      <c r="C58" s="16">
         <v>3.9</v>
       </c>
-      <c r="D58" s="17">
+      <c r="D58" s="16">
         <v>3.7</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E58" s="18">
+        <f t="shared" si="0"/>
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>158</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C59" s="17">
+      <c r="C59" s="16">
         <v>4.4000000000000004</v>
       </c>
-      <c r="D59" s="17">
+      <c r="D59" s="16">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E59" s="18">
+        <f t="shared" si="0"/>
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>159</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C60" s="17">
+      <c r="C60" s="16">
         <v>4.5999999999999996</v>
       </c>
-      <c r="D60" s="17">
+      <c r="D60" s="16">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="E60" s="18">
+        <f t="shared" si="0"/>
+        <v>4.4499999999999993</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>160</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C61" s="17">
+      <c r="C61" s="16">
         <v>3.6</v>
       </c>
-      <c r="D61" s="17">
+      <c r="D61" s="16">
         <v>3.4</v>
+      </c>
+      <c r="E61" s="18">
+        <f t="shared" si="0"/>
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>
@@ -47289,14 +48027,14 @@
       <c r="G1" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="I1" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="J1" s="21" t="s">
-        <v>140</v>
+      <c r="H1" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -47306,30 +48044,30 @@
       <c r="B2" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="23">
+      <c r="C2" s="21">
         <v>10000</v>
       </c>
-      <c r="D2" s="23">
+      <c r="D2" s="21">
         <v>12500</v>
       </c>
-      <c r="E2" s="24">
+      <c r="E2" s="22">
         <v>20</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="22">
         <v>500</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="22">
         <v>50</v>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="20">
         <f>D2-C2</f>
         <v>2500</v>
       </c>
-      <c r="I2" s="25">
+      <c r="I2" s="23">
         <f>(F2+G2)/E2</f>
         <v>27.5</v>
       </c>
-      <c r="J2" s="25">
+      <c r="J2" s="23">
         <f>F2+G2</f>
         <v>550</v>
       </c>
@@ -47341,30 +48079,30 @@
       <c r="B3" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="23">
+      <c r="C3" s="21">
         <v>15000</v>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="21">
         <v>18200</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="22">
         <v>25</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="22">
         <v>700</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="22">
         <v>65</v>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="20">
         <f t="shared" ref="H3:H54" si="0">D3-C3</f>
         <v>3200</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="23">
         <f t="shared" ref="I3:I54" si="1">(F3+G3)/E3</f>
         <v>30.6</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="23">
         <f t="shared" ref="J3:J54" si="2">F3+G3</f>
         <v>765</v>
       </c>
@@ -47376,30 +48114,30 @@
       <c r="B4" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="23">
+      <c r="C4" s="21">
         <v>8000</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="21">
         <v>9500</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="22">
         <v>15</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="22">
         <v>350</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="22">
         <v>30</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="20">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="I4" s="25">
+      <c r="I4" s="23">
         <f t="shared" si="1"/>
         <v>25.333333333333332</v>
       </c>
-      <c r="J4" s="25">
+      <c r="J4" s="23">
         <f t="shared" si="2"/>
         <v>380</v>
       </c>
@@ -47411,30 +48149,30 @@
       <c r="B5" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="23">
+      <c r="C5" s="21">
         <v>20000</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="21">
         <v>22800</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="22">
         <v>30</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="22">
         <v>900</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="22">
         <v>80</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H5" s="20">
         <f t="shared" si="0"/>
         <v>2800</v>
       </c>
-      <c r="I5" s="25">
+      <c r="I5" s="23">
         <f t="shared" si="1"/>
         <v>32.666666666666664</v>
       </c>
-      <c r="J5" s="25">
+      <c r="J5" s="23">
         <f t="shared" si="2"/>
         <v>980</v>
       </c>
@@ -47446,30 +48184,30 @@
       <c r="B6" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="21">
         <v>12000</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="21">
         <v>14500</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="22">
         <v>18</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="22">
         <v>600</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="22">
         <v>55</v>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="20">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="23">
         <f t="shared" si="1"/>
         <v>36.388888888888886</v>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="23">
         <f t="shared" si="2"/>
         <v>655</v>
       </c>
@@ -47481,30 +48219,30 @@
       <c r="B7" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="21">
         <v>25000</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="21">
         <v>27500</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="22">
         <v>35</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="22">
         <v>1.2</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="22">
         <v>100</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="20">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="23">
         <f t="shared" si="1"/>
         <v>2.8914285714285715</v>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="23">
         <f t="shared" si="2"/>
         <v>101.2</v>
       </c>
@@ -47516,30 +48254,30 @@
       <c r="B8" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="21">
         <v>30000</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="21">
         <v>35000</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="22">
         <v>40</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="22">
         <v>1.5</v>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="22">
         <v>120</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="20">
         <f t="shared" si="0"/>
         <v>5000</v>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="23">
         <f t="shared" si="1"/>
         <v>3.0375000000000001</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="23">
         <f t="shared" si="2"/>
         <v>121.5</v>
       </c>
@@ -47551,30 +48289,30 @@
       <c r="B9" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="21">
         <v>18000</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="21">
         <v>20500</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="22">
         <v>28</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="22">
         <v>800</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="22">
         <v>70</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="20">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
-      <c r="I9" s="25">
+      <c r="I9" s="23">
         <f t="shared" si="1"/>
         <v>31.071428571428573</v>
       </c>
-      <c r="J9" s="25">
+      <c r="J9" s="23">
         <f t="shared" si="2"/>
         <v>870</v>
       </c>
@@ -47586,30 +48324,30 @@
       <c r="B10" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="21">
         <v>22000</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="21">
         <v>24800</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="22">
         <v>32</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="22">
         <v>1</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="22">
         <v>90</v>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="20">
         <f t="shared" si="0"/>
         <v>2800</v>
       </c>
-      <c r="I10" s="25">
+      <c r="I10" s="23">
         <f t="shared" si="1"/>
         <v>2.84375</v>
       </c>
-      <c r="J10" s="25">
+      <c r="J10" s="23">
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
@@ -47621,30 +48359,30 @@
       <c r="B11" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="21">
         <v>14000</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="21">
         <v>16500</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="22">
         <v>22</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="22">
         <v>450</v>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="22">
         <v>40</v>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="20">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
-      <c r="I11" s="25">
+      <c r="I11" s="23">
         <f t="shared" si="1"/>
         <v>22.272727272727273</v>
       </c>
-      <c r="J11" s="25">
+      <c r="J11" s="23">
         <f t="shared" si="2"/>
         <v>490</v>
       </c>
@@ -47656,30 +48394,30 @@
       <c r="B12" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="23">
+      <c r="C12" s="21">
         <v>16000</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="21">
         <v>18200</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="22">
         <v>27</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="22">
         <v>700</v>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="22">
         <v>60</v>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="20">
         <f t="shared" si="0"/>
         <v>2200</v>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="23">
         <f t="shared" si="1"/>
         <v>28.148148148148149</v>
       </c>
-      <c r="J12" s="25">
+      <c r="J12" s="23">
         <f t="shared" si="2"/>
         <v>760</v>
       </c>
@@ -47691,30 +48429,30 @@
       <c r="B13" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="23">
+      <c r="C13" s="21">
         <v>11000</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="21">
         <v>12800</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="22">
         <v>21</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="22">
         <v>550</v>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="22">
         <v>45</v>
       </c>
-      <c r="H13" s="22">
+      <c r="H13" s="20">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
-      <c r="I13" s="25">
+      <c r="I13" s="23">
         <f t="shared" si="1"/>
         <v>28.333333333333332</v>
       </c>
-      <c r="J13" s="25">
+      <c r="J13" s="23">
         <f t="shared" si="2"/>
         <v>595</v>
       </c>
@@ -47726,30 +48464,30 @@
       <c r="B14" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="21">
         <v>28000</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="21">
         <v>30500</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="22">
         <v>38</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="22">
         <v>1.2</v>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="22">
         <v>110</v>
       </c>
-      <c r="H14" s="22">
+      <c r="H14" s="20">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
-      <c r="I14" s="25">
+      <c r="I14" s="23">
         <f t="shared" si="1"/>
         <v>2.9263157894736844</v>
       </c>
-      <c r="J14" s="25">
+      <c r="J14" s="23">
         <f t="shared" si="2"/>
         <v>111.2</v>
       </c>
@@ -47761,30 +48499,30 @@
       <c r="B15" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="23">
+      <c r="C15" s="21">
         <v>13000</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="21">
         <v>15500</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="22">
         <v>23</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="22">
         <v>500</v>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="22">
         <v>50</v>
       </c>
-      <c r="H15" s="22">
+      <c r="H15" s="20">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
-      <c r="I15" s="25">
+      <c r="I15" s="23">
         <f t="shared" si="1"/>
         <v>23.913043478260871</v>
       </c>
-      <c r="J15" s="25">
+      <c r="J15" s="23">
         <f t="shared" si="2"/>
         <v>550</v>
       </c>
@@ -47796,30 +48534,30 @@
       <c r="B16" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="23">
+      <c r="C16" s="21">
         <v>17000</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="21">
         <v>19200</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="22">
         <v>29</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="22">
         <v>750</v>
       </c>
-      <c r="G16" s="24">
+      <c r="G16" s="22">
         <v>65</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="20">
         <f t="shared" si="0"/>
         <v>2200</v>
       </c>
-      <c r="I16" s="25">
+      <c r="I16" s="23">
         <f t="shared" si="1"/>
         <v>28.103448275862068</v>
       </c>
-      <c r="J16" s="25">
+      <c r="J16" s="23">
         <f t="shared" si="2"/>
         <v>815</v>
       </c>
@@ -47831,30 +48569,30 @@
       <c r="B17" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="23">
+      <c r="C17" s="21">
         <v>19000</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="21">
         <v>21500</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="22">
         <v>31</v>
       </c>
-      <c r="F17" s="24">
+      <c r="F17" s="22">
         <v>850</v>
       </c>
-      <c r="G17" s="24">
+      <c r="G17" s="22">
         <v>75</v>
       </c>
-      <c r="H17" s="22">
+      <c r="H17" s="20">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="23">
         <f t="shared" si="1"/>
         <v>29.838709677419356</v>
       </c>
-      <c r="J17" s="25">
+      <c r="J17" s="23">
         <f t="shared" si="2"/>
         <v>925</v>
       </c>
@@ -47866,30 +48604,30 @@
       <c r="B18" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="23">
+      <c r="C18" s="21">
         <v>26000</v>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="21">
         <v>28800</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="22">
         <v>37</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="22">
         <v>1</v>
       </c>
-      <c r="G18" s="24">
+      <c r="G18" s="22">
         <v>95</v>
       </c>
-      <c r="H18" s="22">
+      <c r="H18" s="20">
         <f t="shared" si="0"/>
         <v>2800</v>
       </c>
-      <c r="I18" s="25">
+      <c r="I18" s="23">
         <f t="shared" si="1"/>
         <v>2.5945945945945947</v>
       </c>
-      <c r="J18" s="25">
+      <c r="J18" s="23">
         <f t="shared" si="2"/>
         <v>96</v>
       </c>
@@ -47901,30 +48639,30 @@
       <c r="B19" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="23">
+      <c r="C19" s="21">
         <v>24000</v>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="21">
         <v>26500</v>
       </c>
-      <c r="E19" s="24">
+      <c r="E19" s="22">
         <v>35</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="22">
         <v>900</v>
       </c>
-      <c r="G19" s="24">
+      <c r="G19" s="22">
         <v>80</v>
       </c>
-      <c r="H19" s="22">
+      <c r="H19" s="20">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
-      <c r="I19" s="25">
+      <c r="I19" s="23">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="J19" s="25">
+      <c r="J19" s="23">
         <f t="shared" si="2"/>
         <v>980</v>
       </c>
@@ -47936,30 +48674,30 @@
       <c r="B20" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="23">
+      <c r="C20" s="21">
         <v>21000</v>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="21">
         <v>23200</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="22">
         <v>33</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="22">
         <v>800</v>
       </c>
-      <c r="G20" s="24">
+      <c r="G20" s="22">
         <v>70</v>
       </c>
-      <c r="H20" s="22">
+      <c r="H20" s="20">
         <f t="shared" si="0"/>
         <v>2200</v>
       </c>
-      <c r="I20" s="25">
+      <c r="I20" s="23">
         <f t="shared" si="1"/>
         <v>26.363636363636363</v>
       </c>
-      <c r="J20" s="25">
+      <c r="J20" s="23">
         <f t="shared" si="2"/>
         <v>870</v>
       </c>
@@ -47971,30 +48709,30 @@
       <c r="B21" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="C21" s="23">
+      <c r="C21" s="21">
         <v>9000</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="21">
         <v>10500</v>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="22">
         <v>16</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="22">
         <v>300</v>
       </c>
-      <c r="G21" s="24">
+      <c r="G21" s="22">
         <v>25</v>
       </c>
-      <c r="H21" s="22">
+      <c r="H21" s="20">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="I21" s="25">
+      <c r="I21" s="23">
         <f t="shared" si="1"/>
         <v>20.3125</v>
       </c>
-      <c r="J21" s="25">
+      <c r="J21" s="23">
         <f t="shared" si="2"/>
         <v>325</v>
       </c>
@@ -48006,30 +48744,30 @@
       <c r="B22" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="23">
+      <c r="C22" s="21">
         <v>11000</v>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="21">
         <v>13500</v>
       </c>
-      <c r="E22" s="24">
+      <c r="E22" s="22">
         <v>19</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="22">
         <v>400</v>
       </c>
-      <c r="G22" s="24">
+      <c r="G22" s="22">
         <v>45</v>
       </c>
-      <c r="H22" s="22">
+      <c r="H22" s="20">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
-      <c r="I22" s="25">
+      <c r="I22" s="23">
         <f t="shared" si="1"/>
         <v>23.421052631578949</v>
       </c>
-      <c r="J22" s="25">
+      <c r="J22" s="23">
         <f t="shared" si="2"/>
         <v>445</v>
       </c>
@@ -48041,30 +48779,30 @@
       <c r="B23" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="23">
+      <c r="C23" s="21">
         <v>14000</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="21">
         <v>16200</v>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="22">
         <v>24</v>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="22">
         <v>600</v>
       </c>
-      <c r="G23" s="24">
+      <c r="G23" s="22">
         <v>60</v>
       </c>
-      <c r="H23" s="22">
+      <c r="H23" s="20">
         <f t="shared" si="0"/>
         <v>2200</v>
       </c>
-      <c r="I23" s="25">
+      <c r="I23" s="23">
         <f t="shared" si="1"/>
         <v>27.5</v>
       </c>
-      <c r="J23" s="25">
+      <c r="J23" s="23">
         <f t="shared" si="2"/>
         <v>660</v>
       </c>
@@ -48076,30 +48814,30 @@
       <c r="B24" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="C24" s="23">
+      <c r="C24" s="21">
         <v>16000</v>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="21">
         <v>18500</v>
       </c>
-      <c r="E24" s="24">
+      <c r="E24" s="22">
         <v>28</v>
       </c>
-      <c r="F24" s="24">
+      <c r="F24" s="22">
         <v>700</v>
       </c>
-      <c r="G24" s="24">
+      <c r="G24" s="22">
         <v>70</v>
       </c>
-      <c r="H24" s="22">
+      <c r="H24" s="20">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
-      <c r="I24" s="25">
+      <c r="I24" s="23">
         <f t="shared" si="1"/>
         <v>27.5</v>
       </c>
-      <c r="J24" s="25">
+      <c r="J24" s="23">
         <f t="shared" si="2"/>
         <v>770</v>
       </c>
@@ -48111,30 +48849,30 @@
       <c r="B25" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="23">
+      <c r="C25" s="21">
         <v>20000</v>
       </c>
-      <c r="D25" s="23">
+      <c r="D25" s="21">
         <v>22800</v>
       </c>
-      <c r="E25" s="24">
+      <c r="E25" s="22">
         <v>32</v>
       </c>
-      <c r="F25" s="24">
+      <c r="F25" s="22">
         <v>900</v>
       </c>
-      <c r="G25" s="24">
+      <c r="G25" s="22">
         <v>85</v>
       </c>
-      <c r="H25" s="22">
+      <c r="H25" s="20">
         <f t="shared" si="0"/>
         <v>2800</v>
       </c>
-      <c r="I25" s="25">
+      <c r="I25" s="23">
         <f t="shared" si="1"/>
         <v>30.78125</v>
       </c>
-      <c r="J25" s="25">
+      <c r="J25" s="23">
         <f t="shared" si="2"/>
         <v>985</v>
       </c>
@@ -48146,30 +48884,30 @@
       <c r="B26" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="23">
+      <c r="C26" s="21">
         <v>25000</v>
       </c>
-      <c r="D26" s="23">
+      <c r="D26" s="21">
         <v>27500</v>
       </c>
-      <c r="E26" s="24">
+      <c r="E26" s="22">
         <v>37</v>
       </c>
-      <c r="F26" s="24">
+      <c r="F26" s="22">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G26" s="24">
+      <c r="G26" s="22">
         <v>110</v>
       </c>
-      <c r="H26" s="22">
+      <c r="H26" s="20">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
-      <c r="I26" s="25">
+      <c r="I26" s="23">
         <f t="shared" si="1"/>
         <v>3.0027027027027025</v>
       </c>
-      <c r="J26" s="25">
+      <c r="J26" s="23">
         <f t="shared" si="2"/>
         <v>111.1</v>
       </c>
@@ -48181,30 +48919,30 @@
       <c r="B27" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="23">
+      <c r="C27" s="21">
         <v>12000</v>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="21">
         <v>14500</v>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="22">
         <v>22</v>
       </c>
-      <c r="F27" s="24">
+      <c r="F27" s="22">
         <v>450</v>
       </c>
-      <c r="G27" s="24">
+      <c r="G27" s="22">
         <v>40</v>
       </c>
-      <c r="H27" s="22">
+      <c r="H27" s="20">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
-      <c r="I27" s="25">
+      <c r="I27" s="23">
         <f t="shared" si="1"/>
         <v>22.272727272727273</v>
       </c>
-      <c r="J27" s="25">
+      <c r="J27" s="23">
         <f t="shared" si="2"/>
         <v>490</v>
       </c>
@@ -48216,30 +48954,30 @@
       <c r="B28" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="C28" s="23">
+      <c r="C28" s="21">
         <v>18000</v>
       </c>
-      <c r="D28" s="23">
+      <c r="D28" s="21">
         <v>20200</v>
       </c>
-      <c r="E28" s="24">
+      <c r="E28" s="22">
         <v>27</v>
       </c>
-      <c r="F28" s="24">
+      <c r="F28" s="22">
         <v>700</v>
       </c>
-      <c r="G28" s="24">
+      <c r="G28" s="22">
         <v>65</v>
       </c>
-      <c r="H28" s="22">
+      <c r="H28" s="20">
         <f t="shared" si="0"/>
         <v>2200</v>
       </c>
-      <c r="I28" s="25">
+      <c r="I28" s="23">
         <f t="shared" si="1"/>
         <v>28.333333333333332</v>
       </c>
-      <c r="J28" s="25">
+      <c r="J28" s="23">
         <f t="shared" si="2"/>
         <v>765</v>
       </c>
@@ -48251,30 +48989,30 @@
       <c r="B29" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="C29" s="23">
+      <c r="C29" s="21">
         <v>23000</v>
       </c>
-      <c r="D29" s="23">
+      <c r="D29" s="21">
         <v>25500</v>
       </c>
-      <c r="E29" s="24">
+      <c r="E29" s="22">
         <v>33</v>
       </c>
-      <c r="F29" s="24">
+      <c r="F29" s="22">
         <v>800</v>
       </c>
-      <c r="G29" s="24">
+      <c r="G29" s="22">
         <v>75</v>
       </c>
-      <c r="H29" s="22">
+      <c r="H29" s="20">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
-      <c r="I29" s="25">
+      <c r="I29" s="23">
         <f t="shared" si="1"/>
         <v>26.515151515151516</v>
       </c>
-      <c r="J29" s="25">
+      <c r="J29" s="23">
         <f t="shared" si="2"/>
         <v>875</v>
       </c>
@@ -48286,30 +49024,30 @@
       <c r="B30" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="C30" s="23">
+      <c r="C30" s="21">
         <v>28000</v>
       </c>
-      <c r="D30" s="23">
+      <c r="D30" s="21">
         <v>30800</v>
       </c>
-      <c r="E30" s="24">
+      <c r="E30" s="22">
         <v>39</v>
       </c>
-      <c r="F30" s="24">
+      <c r="F30" s="22">
         <v>1</v>
       </c>
-      <c r="G30" s="24">
+      <c r="G30" s="22">
         <v>90</v>
       </c>
-      <c r="H30" s="22">
+      <c r="H30" s="20">
         <f t="shared" si="0"/>
         <v>2800</v>
       </c>
-      <c r="I30" s="25">
+      <c r="I30" s="23">
         <f t="shared" si="1"/>
         <v>2.3333333333333335</v>
       </c>
-      <c r="J30" s="25">
+      <c r="J30" s="23">
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
@@ -48321,30 +49059,30 @@
       <c r="B31" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="C31" s="23">
+      <c r="C31" s="21">
         <v>15000</v>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="21">
         <v>17500</v>
       </c>
-      <c r="E31" s="24">
+      <c r="E31" s="22">
         <v>25</v>
       </c>
-      <c r="F31" s="24">
+      <c r="F31" s="22">
         <v>550</v>
       </c>
-      <c r="G31" s="24">
+      <c r="G31" s="22">
         <v>50</v>
       </c>
-      <c r="H31" s="22">
+      <c r="H31" s="20">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
-      <c r="I31" s="25">
+      <c r="I31" s="23">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="J31" s="25">
+      <c r="J31" s="23">
         <f t="shared" si="2"/>
         <v>600</v>
       </c>
@@ -48356,30 +49094,30 @@
       <c r="B32" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C32" s="23">
+      <c r="C32" s="21">
         <v>19000</v>
       </c>
-      <c r="D32" s="23">
+      <c r="D32" s="21">
         <v>21200</v>
       </c>
-      <c r="E32" s="24">
+      <c r="E32" s="22">
         <v>29</v>
       </c>
-      <c r="F32" s="24">
+      <c r="F32" s="22">
         <v>600</v>
       </c>
-      <c r="G32" s="24">
+      <c r="G32" s="22">
         <v>55</v>
       </c>
-      <c r="H32" s="22">
+      <c r="H32" s="20">
         <f t="shared" si="0"/>
         <v>2200</v>
       </c>
-      <c r="I32" s="25">
+      <c r="I32" s="23">
         <f t="shared" si="1"/>
         <v>22.586206896551722</v>
       </c>
-      <c r="J32" s="25">
+      <c r="J32" s="23">
         <f t="shared" si="2"/>
         <v>655</v>
       </c>
@@ -48391,30 +49129,30 @@
       <c r="B33" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="C33" s="23">
+      <c r="C33" s="21">
         <v>24000</v>
       </c>
-      <c r="D33" s="23">
+      <c r="D33" s="21">
         <v>26800</v>
       </c>
-      <c r="E33" s="24">
+      <c r="E33" s="22">
         <v>35</v>
       </c>
-      <c r="F33" s="24">
+      <c r="F33" s="22">
         <v>700</v>
       </c>
-      <c r="G33" s="24">
+      <c r="G33" s="22">
         <v>60</v>
       </c>
-      <c r="H33" s="22">
+      <c r="H33" s="20">
         <f t="shared" si="0"/>
         <v>2800</v>
       </c>
-      <c r="I33" s="25">
+      <c r="I33" s="23">
         <f t="shared" si="1"/>
         <v>21.714285714285715</v>
       </c>
-      <c r="J33" s="25">
+      <c r="J33" s="23">
         <f t="shared" si="2"/>
         <v>760</v>
       </c>
@@ -48426,30 +49164,30 @@
       <c r="B34" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="C34" s="23">
+      <c r="C34" s="21">
         <v>30000</v>
       </c>
-      <c r="D34" s="23">
+      <c r="D34" s="21">
         <v>32500</v>
       </c>
-      <c r="E34" s="24">
+      <c r="E34" s="22">
         <v>40</v>
       </c>
-      <c r="F34" s="24">
+      <c r="F34" s="22">
         <v>800</v>
       </c>
-      <c r="G34" s="24">
+      <c r="G34" s="22">
         <v>65</v>
       </c>
-      <c r="H34" s="22">
+      <c r="H34" s="20">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
-      <c r="I34" s="25">
+      <c r="I34" s="23">
         <f t="shared" si="1"/>
         <v>21.625</v>
       </c>
-      <c r="J34" s="25">
+      <c r="J34" s="23">
         <f t="shared" si="2"/>
         <v>865</v>
       </c>
@@ -48461,30 +49199,30 @@
       <c r="B35" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="C35" s="23">
+      <c r="C35" s="21">
         <v>10000</v>
       </c>
-      <c r="D35" s="23">
+      <c r="D35" s="21">
         <v>11800</v>
       </c>
-      <c r="E35" s="24">
+      <c r="E35" s="22">
         <v>18</v>
       </c>
-      <c r="F35" s="24">
+      <c r="F35" s="22">
         <v>350</v>
       </c>
-      <c r="G35" s="24">
+      <c r="G35" s="22">
         <v>30</v>
       </c>
-      <c r="H35" s="22">
+      <c r="H35" s="20">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
-      <c r="I35" s="25">
+      <c r="I35" s="23">
         <f t="shared" si="1"/>
         <v>21.111111111111111</v>
       </c>
-      <c r="J35" s="25">
+      <c r="J35" s="23">
         <f t="shared" si="2"/>
         <v>380</v>
       </c>
@@ -48496,30 +49234,30 @@
       <c r="B36" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C36" s="23">
+      <c r="C36" s="21">
         <v>14000</v>
       </c>
-      <c r="D36" s="23">
+      <c r="D36" s="21">
         <v>15500</v>
       </c>
-      <c r="E36" s="24">
+      <c r="E36" s="22">
         <v>22</v>
       </c>
-      <c r="F36" s="24">
+      <c r="F36" s="22">
         <v>400</v>
       </c>
-      <c r="G36" s="24">
+      <c r="G36" s="22">
         <v>35</v>
       </c>
-      <c r="H36" s="22">
+      <c r="H36" s="20">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="I36" s="25">
+      <c r="I36" s="23">
         <f t="shared" si="1"/>
         <v>19.772727272727273</v>
       </c>
-      <c r="J36" s="25">
+      <c r="J36" s="23">
         <f t="shared" si="2"/>
         <v>435</v>
       </c>
@@ -48531,30 +49269,30 @@
       <c r="B37" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C37" s="23">
+      <c r="C37" s="21">
         <v>18000</v>
       </c>
-      <c r="D37" s="23">
+      <c r="D37" s="21">
         <v>19800</v>
       </c>
-      <c r="E37" s="24">
+      <c r="E37" s="22">
         <v>27</v>
       </c>
-      <c r="F37" s="24">
+      <c r="F37" s="22">
         <v>450</v>
       </c>
-      <c r="G37" s="24">
+      <c r="G37" s="22">
         <v>40</v>
       </c>
-      <c r="H37" s="22">
+      <c r="H37" s="20">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
-      <c r="I37" s="25">
+      <c r="I37" s="23">
         <f t="shared" si="1"/>
         <v>18.148148148148149</v>
       </c>
-      <c r="J37" s="25">
+      <c r="J37" s="23">
         <f t="shared" si="2"/>
         <v>490</v>
       </c>
@@ -48566,30 +49304,30 @@
       <c r="B38" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="C38" s="23">
+      <c r="C38" s="21">
         <v>22000</v>
       </c>
-      <c r="D38" s="23">
+      <c r="D38" s="21">
         <v>24500</v>
       </c>
-      <c r="E38" s="24">
+      <c r="E38" s="22">
         <v>32</v>
       </c>
-      <c r="F38" s="24">
+      <c r="F38" s="22">
         <v>500</v>
       </c>
-      <c r="G38" s="24">
+      <c r="G38" s="22">
         <v>45</v>
       </c>
-      <c r="H38" s="22">
+      <c r="H38" s="20">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
-      <c r="I38" s="25">
+      <c r="I38" s="23">
         <f t="shared" si="1"/>
         <v>17.03125</v>
       </c>
-      <c r="J38" s="25">
+      <c r="J38" s="23">
         <f t="shared" si="2"/>
         <v>545</v>
       </c>
@@ -48601,30 +49339,30 @@
       <c r="B39" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="C39" s="23">
+      <c r="C39" s="21">
         <v>26000</v>
       </c>
-      <c r="D39" s="23">
+      <c r="D39" s="21">
         <v>28200</v>
       </c>
-      <c r="E39" s="24">
+      <c r="E39" s="22">
         <v>37</v>
       </c>
-      <c r="F39" s="24">
+      <c r="F39" s="22">
         <v>550</v>
       </c>
-      <c r="G39" s="24">
+      <c r="G39" s="22">
         <v>50</v>
       </c>
-      <c r="H39" s="22">
+      <c r="H39" s="20">
         <f t="shared" si="0"/>
         <v>2200</v>
       </c>
-      <c r="I39" s="25">
+      <c r="I39" s="23">
         <f t="shared" si="1"/>
         <v>16.216216216216218</v>
       </c>
-      <c r="J39" s="25">
+      <c r="J39" s="23">
         <f t="shared" si="2"/>
         <v>600</v>
       </c>
@@ -48636,30 +49374,30 @@
       <c r="B40" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="C40" s="23">
+      <c r="C40" s="21">
         <v>30000</v>
       </c>
-      <c r="D40" s="23">
+      <c r="D40" s="21">
         <v>31500</v>
       </c>
-      <c r="E40" s="24">
+      <c r="E40" s="22">
         <v>40</v>
       </c>
-      <c r="F40" s="24">
+      <c r="F40" s="22">
         <v>600</v>
       </c>
-      <c r="G40" s="24">
+      <c r="G40" s="22">
         <v>55</v>
       </c>
-      <c r="H40" s="22">
+      <c r="H40" s="20">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="I40" s="25">
+      <c r="I40" s="23">
         <f t="shared" si="1"/>
         <v>16.375</v>
       </c>
-      <c r="J40" s="25">
+      <c r="J40" s="23">
         <f t="shared" si="2"/>
         <v>655</v>
       </c>
@@ -48671,30 +49409,30 @@
       <c r="B41" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="C41" s="23">
+      <c r="C41" s="21">
         <v>15000</v>
       </c>
-      <c r="D41" s="23">
+      <c r="D41" s="21">
         <v>16800</v>
       </c>
-      <c r="E41" s="24">
+      <c r="E41" s="22">
         <v>25</v>
       </c>
-      <c r="F41" s="24">
+      <c r="F41" s="22">
         <v>650</v>
       </c>
-      <c r="G41" s="24">
+      <c r="G41" s="22">
         <v>60</v>
       </c>
-      <c r="H41" s="22">
+      <c r="H41" s="20">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
-      <c r="I41" s="25">
+      <c r="I41" s="23">
         <f t="shared" si="1"/>
         <v>28.4</v>
       </c>
-      <c r="J41" s="25">
+      <c r="J41" s="23">
         <f t="shared" si="2"/>
         <v>710</v>
       </c>
@@ -48706,30 +49444,30 @@
       <c r="B42" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="C42" s="23">
+      <c r="C42" s="21">
         <v>20000</v>
       </c>
-      <c r="D42" s="23">
+      <c r="D42" s="21">
         <v>21500</v>
       </c>
-      <c r="E42" s="24">
+      <c r="E42" s="22">
         <v>30</v>
       </c>
-      <c r="F42" s="24">
+      <c r="F42" s="22">
         <v>700</v>
       </c>
-      <c r="G42" s="24">
+      <c r="G42" s="22">
         <v>65</v>
       </c>
-      <c r="H42" s="22">
+      <c r="H42" s="20">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="I42" s="25">
+      <c r="I42" s="23">
         <f t="shared" si="1"/>
         <v>25.5</v>
       </c>
-      <c r="J42" s="25">
+      <c r="J42" s="23">
         <f t="shared" si="2"/>
         <v>765</v>
       </c>
@@ -48741,30 +49479,30 @@
       <c r="B43" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="C43" s="23">
+      <c r="C43" s="21">
         <v>25000</v>
       </c>
-      <c r="D43" s="23">
+      <c r="D43" s="21">
         <v>26800</v>
       </c>
-      <c r="E43" s="24">
+      <c r="E43" s="22">
         <v>35</v>
       </c>
-      <c r="F43" s="24">
+      <c r="F43" s="22">
         <v>750</v>
       </c>
-      <c r="G43" s="24">
+      <c r="G43" s="22">
         <v>70</v>
       </c>
-      <c r="H43" s="22">
+      <c r="H43" s="20">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
-      <c r="I43" s="25">
+      <c r="I43" s="23">
         <f t="shared" si="1"/>
         <v>23.428571428571427</v>
       </c>
-      <c r="J43" s="25">
+      <c r="J43" s="23">
         <f t="shared" si="2"/>
         <v>820</v>
       </c>
@@ -48776,30 +49514,30 @@
       <c r="B44" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="C44" s="23">
+      <c r="C44" s="21">
         <v>30000</v>
       </c>
-      <c r="D44" s="23">
+      <c r="D44" s="21">
         <v>31500</v>
       </c>
-      <c r="E44" s="24">
+      <c r="E44" s="22">
         <v>40</v>
       </c>
-      <c r="F44" s="24">
+      <c r="F44" s="22">
         <v>800</v>
       </c>
-      <c r="G44" s="24">
+      <c r="G44" s="22">
         <v>75</v>
       </c>
-      <c r="H44" s="22">
+      <c r="H44" s="20">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="I44" s="25">
+      <c r="I44" s="23">
         <f t="shared" si="1"/>
         <v>21.875</v>
       </c>
-      <c r="J44" s="25">
+      <c r="J44" s="23">
         <f t="shared" si="2"/>
         <v>875</v>
       </c>
@@ -48811,30 +49549,30 @@
       <c r="B45" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="C45" s="23">
+      <c r="C45" s="21">
         <v>12000</v>
       </c>
-      <c r="D45" s="23">
+      <c r="D45" s="21">
         <v>13200</v>
       </c>
-      <c r="E45" s="24">
+      <c r="E45" s="22">
         <v>20</v>
       </c>
-      <c r="F45" s="24">
+      <c r="F45" s="22">
         <v>500</v>
       </c>
-      <c r="G45" s="24">
+      <c r="G45" s="22">
         <v>45</v>
       </c>
-      <c r="H45" s="22">
+      <c r="H45" s="20">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="I45" s="25">
+      <c r="I45" s="23">
         <f t="shared" si="1"/>
         <v>27.25</v>
       </c>
-      <c r="J45" s="25">
+      <c r="J45" s="23">
         <f t="shared" si="2"/>
         <v>545</v>
       </c>
@@ -48846,30 +49584,30 @@
       <c r="B46" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="C46" s="23">
+      <c r="C46" s="21">
         <v>17000</v>
       </c>
-      <c r="D46" s="23">
+      <c r="D46" s="21">
         <v>18500</v>
       </c>
-      <c r="E46" s="24">
+      <c r="E46" s="22">
         <v>25</v>
       </c>
-      <c r="F46" s="24">
+      <c r="F46" s="22">
         <v>550</v>
       </c>
-      <c r="G46" s="24">
+      <c r="G46" s="22">
         <v>50</v>
       </c>
-      <c r="H46" s="22">
+      <c r="H46" s="20">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="I46" s="25">
+      <c r="I46" s="23">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="J46" s="25">
+      <c r="J46" s="23">
         <f t="shared" si="2"/>
         <v>600</v>
       </c>
@@ -48881,30 +49619,30 @@
       <c r="B47" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="C47" s="23">
+      <c r="C47" s="21">
         <v>22000</v>
       </c>
-      <c r="D47" s="23">
+      <c r="D47" s="21">
         <v>23800</v>
       </c>
-      <c r="E47" s="24">
+      <c r="E47" s="22">
         <v>30</v>
       </c>
-      <c r="F47" s="24">
+      <c r="F47" s="22">
         <v>600</v>
       </c>
-      <c r="G47" s="24">
+      <c r="G47" s="22">
         <v>55</v>
       </c>
-      <c r="H47" s="22">
+      <c r="H47" s="20">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
-      <c r="I47" s="25">
+      <c r="I47" s="23">
         <f t="shared" si="1"/>
         <v>21.833333333333332</v>
       </c>
-      <c r="J47" s="25">
+      <c r="J47" s="23">
         <f t="shared" si="2"/>
         <v>655</v>
       </c>
@@ -48916,30 +49654,30 @@
       <c r="B48" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="C48" s="23">
+      <c r="C48" s="21">
         <v>27000</v>
       </c>
-      <c r="D48" s="23">
+      <c r="D48" s="21">
         <v>28500</v>
       </c>
-      <c r="E48" s="24">
+      <c r="E48" s="22">
         <v>35</v>
       </c>
-      <c r="F48" s="24">
+      <c r="F48" s="22">
         <v>650</v>
       </c>
-      <c r="G48" s="24">
+      <c r="G48" s="22">
         <v>60</v>
       </c>
-      <c r="H48" s="22">
+      <c r="H48" s="20">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="I48" s="25">
+      <c r="I48" s="23">
         <f t="shared" si="1"/>
         <v>20.285714285714285</v>
       </c>
-      <c r="J48" s="25">
+      <c r="J48" s="23">
         <f t="shared" si="2"/>
         <v>710</v>
       </c>
@@ -48951,30 +49689,30 @@
       <c r="B49" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="C49" s="23">
+      <c r="C49" s="21">
         <v>32000</v>
       </c>
-      <c r="D49" s="23">
+      <c r="D49" s="21">
         <v>33500</v>
       </c>
-      <c r="E49" s="24">
+      <c r="E49" s="22">
         <v>40</v>
       </c>
-      <c r="F49" s="24">
+      <c r="F49" s="22">
         <v>700</v>
       </c>
-      <c r="G49" s="24">
+      <c r="G49" s="22">
         <v>65</v>
       </c>
-      <c r="H49" s="22">
+      <c r="H49" s="20">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="I49" s="25">
+      <c r="I49" s="23">
         <f t="shared" si="1"/>
         <v>19.125</v>
       </c>
-      <c r="J49" s="25">
+      <c r="J49" s="23">
         <f t="shared" si="2"/>
         <v>765</v>
       </c>
@@ -48986,30 +49724,30 @@
       <c r="B50" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="C50" s="23">
+      <c r="C50" s="21">
         <v>15000</v>
       </c>
-      <c r="D50" s="23">
+      <c r="D50" s="21">
         <v>16200</v>
       </c>
-      <c r="E50" s="24">
+      <c r="E50" s="22">
         <v>22</v>
       </c>
-      <c r="F50" s="24">
+      <c r="F50" s="22">
         <v>750</v>
       </c>
-      <c r="G50" s="24">
+      <c r="G50" s="22">
         <v>70</v>
       </c>
-      <c r="H50" s="22">
+      <c r="H50" s="20">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="I50" s="25">
+      <c r="I50" s="23">
         <f t="shared" si="1"/>
         <v>37.272727272727273</v>
       </c>
-      <c r="J50" s="25">
+      <c r="J50" s="23">
         <f t="shared" si="2"/>
         <v>820</v>
       </c>
@@ -49021,30 +49759,30 @@
       <c r="B51" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="C51" s="23">
+      <c r="C51" s="21">
         <v>20000</v>
       </c>
-      <c r="D51" s="23">
+      <c r="D51" s="21">
         <v>21500</v>
       </c>
-      <c r="E51" s="24">
+      <c r="E51" s="22">
         <v>27</v>
       </c>
-      <c r="F51" s="24">
+      <c r="F51" s="22">
         <v>800</v>
       </c>
-      <c r="G51" s="24">
+      <c r="G51" s="22">
         <v>75</v>
       </c>
-      <c r="H51" s="22">
+      <c r="H51" s="20">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="I51" s="25">
+      <c r="I51" s="23">
         <f t="shared" si="1"/>
         <v>32.407407407407405</v>
       </c>
-      <c r="J51" s="25">
+      <c r="J51" s="23">
         <f t="shared" si="2"/>
         <v>875</v>
       </c>
@@ -49056,30 +49794,30 @@
       <c r="B52" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="C52" s="23">
+      <c r="C52" s="21">
         <v>25000</v>
       </c>
-      <c r="D52" s="23">
+      <c r="D52" s="21">
         <v>26800</v>
       </c>
-      <c r="E52" s="24">
+      <c r="E52" s="22">
         <v>32</v>
       </c>
-      <c r="F52" s="24">
+      <c r="F52" s="22">
         <v>850</v>
       </c>
-      <c r="G52" s="24">
+      <c r="G52" s="22">
         <v>80</v>
       </c>
-      <c r="H52" s="22">
+      <c r="H52" s="20">
         <f t="shared" si="0"/>
         <v>1800</v>
       </c>
-      <c r="I52" s="25">
+      <c r="I52" s="23">
         <f t="shared" si="1"/>
         <v>29.0625</v>
       </c>
-      <c r="J52" s="25">
+      <c r="J52" s="23">
         <f t="shared" si="2"/>
         <v>930</v>
       </c>
@@ -49091,30 +49829,30 @@
       <c r="B53" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="C53" s="23">
+      <c r="C53" s="21">
         <v>30000</v>
       </c>
-      <c r="D53" s="23">
+      <c r="D53" s="21">
         <v>31500</v>
       </c>
-      <c r="E53" s="24">
+      <c r="E53" s="22">
         <v>37</v>
       </c>
-      <c r="F53" s="24">
+      <c r="F53" s="22">
         <v>900</v>
       </c>
-      <c r="G53" s="24">
+      <c r="G53" s="22">
         <v>85</v>
       </c>
-      <c r="H53" s="22">
+      <c r="H53" s="20">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="I53" s="25">
+      <c r="I53" s="23">
         <f t="shared" si="1"/>
         <v>26.621621621621621</v>
       </c>
-      <c r="J53" s="25">
+      <c r="J53" s="23">
         <f t="shared" si="2"/>
         <v>985</v>
       </c>
@@ -49126,30 +49864,30 @@
       <c r="B54" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="C54" s="23">
+      <c r="C54" s="21">
         <v>10000</v>
       </c>
-      <c r="D54" s="23">
+      <c r="D54" s="21">
         <v>11200</v>
       </c>
-      <c r="E54" s="24">
+      <c r="E54" s="22">
         <v>18</v>
       </c>
-      <c r="F54" s="24">
+      <c r="F54" s="22">
         <v>400</v>
       </c>
-      <c r="G54" s="24">
+      <c r="G54" s="22">
         <v>40</v>
       </c>
-      <c r="H54" s="22">
+      <c r="H54" s="20">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="I54" s="25">
+      <c r="I54" s="23">
         <f t="shared" si="1"/>
         <v>24.444444444444443</v>
       </c>
-      <c r="J54" s="25">
+      <c r="J54" s="23">
         <f t="shared" si="2"/>
         <v>440</v>
       </c>
